--- a/data/clean/AR_methods.xlsx
+++ b/data/clean/AR_methods.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thema\OneDrive\Documents\dissertation\survey\github\data\clean\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmcgreal\Documents\dissertation\survey\data\clean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17345127-6C5A-48B1-A089-70A736047BA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D9F221-18A7-496F-86F4-63BBD64F6F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="24240" windowHeight="13140" activeTab="1" xr2:uid="{70F81E01-4849-42CD-AB9B-9414582B1355}"/>
+    <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{70F81E01-4849-42CD-AB9B-9414582B1355}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="36">
   <si>
     <t>Chinook</t>
   </si>
@@ -112,13 +123,28 @@
     <t>Species</t>
   </si>
   <si>
-    <t>Relative Bias</t>
-  </si>
-  <si>
     <t>New Bias</t>
   </si>
   <si>
     <t>NewVar</t>
+  </si>
+  <si>
+    <t>Afull Bias</t>
+  </si>
+  <si>
+    <t>Afull Var</t>
+  </si>
+  <si>
+    <t>BreaksAful</t>
+  </si>
+  <si>
+    <t>BreaksNew</t>
+  </si>
+  <si>
+    <t>Diff</t>
+  </si>
+  <si>
+    <t>Precision</t>
   </si>
 </sst>
 </file>
@@ -160,9 +186,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -181,9 +208,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -221,7 +248,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -327,7 +354,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -469,7 +496,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -477,14 +504,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B32334F8-B11A-4935-8120-0620CA328AA2}">
-  <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="75.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="75.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>12</v>
       </c>
@@ -498,13 +525,28 @@
         <v>3</v>
       </c>
       <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
         <v>29</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -526,8 +568,26 @@
       <c r="H2">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J2">
+        <v>-2.08</v>
+      </c>
+      <c r="K2">
+        <v>3.4</v>
+      </c>
+      <c r="M2">
+        <f>G2-G3</f>
+        <v>-1.75</v>
+      </c>
+      <c r="N2">
+        <f>J2-J3</f>
+        <v>-1.7200000000000002</v>
+      </c>
+      <c r="O2">
+        <f>ABS(M2-N2)</f>
+        <v>2.9999999999999805E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>9</v>
       </c>
@@ -546,8 +606,26 @@
       <c r="H3">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J3">
+        <v>-0.36</v>
+      </c>
+      <c r="K3">
+        <v>0.12</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M10" si="0">G3-G4</f>
+        <v>-0.27</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N10" si="1">J3-J4</f>
+        <v>-0.27999999999999997</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O10" si="2">ABS(M3-N3)</f>
+        <v>9.9999999999999534E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>11</v>
       </c>
@@ -564,10 +642,28 @@
         <v>0.27</v>
       </c>
       <c r="H4">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+        <v>0.11</v>
+      </c>
+      <c r="J4">
+        <v>-0.08</v>
+      </c>
+      <c r="K4">
+        <v>0.11</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="0"/>
+        <v>-0.49</v>
+      </c>
+      <c r="N4">
+        <f t="shared" si="1"/>
+        <v>-0.5</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>16</v>
       </c>
@@ -586,8 +682,26 @@
       <c r="H5">
         <v>0.36</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J5">
+        <v>0.42</v>
+      </c>
+      <c r="K5">
+        <v>0.36</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="0"/>
+        <v>0.87</v>
+      </c>
+      <c r="N5">
+        <f t="shared" si="1"/>
+        <v>0.87</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>17</v>
       </c>
@@ -606,8 +720,26 @@
       <c r="H6">
         <v>0.28000000000000003</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J6">
+        <v>-0.45</v>
+      </c>
+      <c r="K6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="0"/>
+        <v>1.8999999999999997</v>
+      </c>
+      <c r="N6">
+        <f t="shared" si="1"/>
+        <v>1.9000000000000001</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="2"/>
+        <v>4.4408920985006262E-16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>18</v>
       </c>
@@ -626,8 +758,26 @@
       <c r="H7">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J7">
+        <v>-2.35</v>
+      </c>
+      <c r="K7">
+        <v>0.3</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="0"/>
+        <v>-1.8699999999999997</v>
+      </c>
+      <c r="N7">
+        <f t="shared" si="1"/>
+        <v>-1.86</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="2"/>
+        <v>9.9999999999995648E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>21</v>
       </c>
@@ -646,8 +796,26 @@
       <c r="H8">
         <v>0.42</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J8">
+        <v>-0.49</v>
+      </c>
+      <c r="K8">
+        <v>0.42</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="0"/>
+        <v>-1.75</v>
+      </c>
+      <c r="N8">
+        <f t="shared" si="1"/>
+        <v>-1.8</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="2"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>22</v>
       </c>
@@ -666,8 +834,26 @@
       <c r="H9">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J9">
+        <v>1.31</v>
+      </c>
+      <c r="K9">
+        <v>0.1</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="0"/>
+        <v>1.28</v>
+      </c>
+      <c r="N9">
+        <f t="shared" si="1"/>
+        <v>1.33</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="2"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>29</v>
       </c>
@@ -686,8 +872,26 @@
       <c r="H10">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J10">
+        <v>-0.02</v>
+      </c>
+      <c r="K10">
+        <v>0.18</v>
+      </c>
+      <c r="M10">
+        <f>G10-G2</f>
+        <v>2.08</v>
+      </c>
+      <c r="N10">
+        <f>J10-J2</f>
+        <v>2.06</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="2"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -709,8 +913,26 @@
       <c r="H12">
         <v>0.54</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J12">
+        <v>-0.05</v>
+      </c>
+      <c r="K12">
+        <v>0.54</v>
+      </c>
+      <c r="M12">
+        <f>G12-G13</f>
+        <v>-0.25</v>
+      </c>
+      <c r="N12">
+        <f>J12-J13</f>
+        <v>-0.25</v>
+      </c>
+      <c r="O12">
+        <f>ABS(M12-N12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>2</v>
       </c>
@@ -729,8 +951,26 @@
       <c r="H13">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J13">
+        <v>0.2</v>
+      </c>
+      <c r="K13">
+        <v>0.51</v>
+      </c>
+      <c r="M13">
+        <f t="shared" ref="M13:M19" si="3">G13-G14</f>
+        <v>0.34000000000000008</v>
+      </c>
+      <c r="N13">
+        <f t="shared" ref="N13:N19" si="4">J13-J14</f>
+        <v>0.33</v>
+      </c>
+      <c r="O13">
+        <f t="shared" ref="O13:O19" si="5">ABS(M13-N13)</f>
+        <v>1.0000000000000064E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>3</v>
       </c>
@@ -749,8 +989,26 @@
       <c r="H14">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J14">
+        <v>-0.13</v>
+      </c>
+      <c r="K14">
+        <v>0.4</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="3"/>
+        <v>-0.48</v>
+      </c>
+      <c r="N14">
+        <f t="shared" si="4"/>
+        <v>-0.47000000000000003</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="5"/>
+        <v>9.9999999999999534E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>4</v>
       </c>
@@ -769,8 +1027,26 @@
       <c r="H15">
         <v>0.41</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J15">
+        <v>0.34</v>
+      </c>
+      <c r="K15">
+        <v>0.41</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="3"/>
+        <v>0.87999999999999989</v>
+      </c>
+      <c r="N15">
+        <f t="shared" si="4"/>
+        <v>0.87000000000000011</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="5"/>
+        <v>9.9999999999997868E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>7</v>
       </c>
@@ -789,8 +1065,26 @@
       <c r="H16">
         <v>0.36</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J16">
+        <v>-0.53</v>
+      </c>
+      <c r="K16">
+        <v>0.36</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="3"/>
+        <v>-0.19</v>
+      </c>
+      <c r="N16">
+        <f t="shared" si="4"/>
+        <v>-0.19</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>8</v>
       </c>
@@ -809,8 +1103,26 @@
       <c r="H17">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J17">
+        <v>-0.34</v>
+      </c>
+      <c r="K17">
+        <v>0.3</v>
+      </c>
+      <c r="M17">
+        <f t="shared" si="3"/>
+        <v>0.26</v>
+      </c>
+      <c r="N17">
+        <f t="shared" si="4"/>
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="5"/>
+        <v>1.9999999999999962E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>9</v>
       </c>
@@ -829,8 +1141,26 @@
       <c r="H18">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J18">
+        <v>-0.62</v>
+      </c>
+      <c r="K18">
+        <v>0.27</v>
+      </c>
+      <c r="M18">
+        <f t="shared" si="3"/>
+        <v>-0.84</v>
+      </c>
+      <c r="N18">
+        <f t="shared" si="4"/>
+        <v>-0.81</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="5"/>
+        <v>2.9999999999999916E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>10</v>
       </c>
@@ -849,8 +1179,26 @@
       <c r="H19">
         <v>0.13</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J19">
+        <v>0.19</v>
+      </c>
+      <c r="K19">
+        <v>0.13</v>
+      </c>
+      <c r="M19">
+        <f t="shared" si="3"/>
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="N19">
+        <f t="shared" si="4"/>
+        <v>-0.60000000000000009</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="5"/>
+        <v>3.0000000000000138E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B20">
         <v>11</v>
       </c>
@@ -869,8 +1217,26 @@
       <c r="H20">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J20">
+        <v>0.79</v>
+      </c>
+      <c r="K20">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="M20">
+        <f t="shared" ref="M20:M21" si="6">G20-G21</f>
+        <v>-0.21999999999999997</v>
+      </c>
+      <c r="N20">
+        <f t="shared" ref="N20:N21" si="7">J20-J21</f>
+        <v>-0.20999999999999996</v>
+      </c>
+      <c r="O20">
+        <f t="shared" ref="O20:O21" si="8">ABS(M20-N20)</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B21">
         <v>19</v>
       </c>
@@ -889,8 +1255,26 @@
       <c r="H21">
         <v>0.24</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>0.24</v>
+      </c>
+      <c r="M21">
+        <f>G21-G12</f>
+        <v>1.0699999999999998</v>
+      </c>
+      <c r="N21">
+        <f>J21-J12</f>
+        <v>1.05</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="8"/>
+        <v>1.9999999999999796E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -912,8 +1296,26 @@
       <c r="H23">
         <v>0.09</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J23">
+        <v>-0.11</v>
+      </c>
+      <c r="K23">
+        <v>0.09</v>
+      </c>
+      <c r="M23">
+        <f>G23-G24</f>
+        <v>-0.53</v>
+      </c>
+      <c r="N23">
+        <f>J23-J24</f>
+        <v>-0.53</v>
+      </c>
+      <c r="O23">
+        <f>ABS(M23-N23)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>11</v>
       </c>
@@ -932,8 +1334,26 @@
       <c r="H24">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J24">
+        <v>0.42</v>
+      </c>
+      <c r="K24">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="M24">
+        <f t="shared" ref="M24:M30" si="9">G24-G25</f>
+        <v>1.77</v>
+      </c>
+      <c r="N24">
+        <f t="shared" ref="N24:N30" si="10">J24-J25</f>
+        <v>1.74</v>
+      </c>
+      <c r="O24">
+        <f t="shared" ref="O24:O30" si="11">ABS(M24-N24)</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>14</v>
       </c>
@@ -952,8 +1372,26 @@
       <c r="H25">
         <v>0.11</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J25">
+        <v>-1.32</v>
+      </c>
+      <c r="K25">
+        <v>0.11</v>
+      </c>
+      <c r="M25">
+        <f t="shared" si="9"/>
+        <v>-1.07</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="10"/>
+        <v>-1.05</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="11"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B26">
         <v>15</v>
       </c>
@@ -972,8 +1410,26 @@
       <c r="H26">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J26">
+        <v>-0.27</v>
+      </c>
+      <c r="K26">
+        <v>0.15</v>
+      </c>
+      <c r="M26">
+        <f t="shared" si="9"/>
+        <v>-0.54</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="10"/>
+        <v>-0.54</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B27">
         <v>16</v>
       </c>
@@ -992,8 +1448,26 @@
       <c r="H27">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J27">
+        <v>0.27</v>
+      </c>
+      <c r="K27">
+        <v>0.1</v>
+      </c>
+      <c r="M27">
+        <f t="shared" si="9"/>
+        <v>0.33999999999999997</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="10"/>
+        <v>0.34</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="11"/>
+        <v>5.5511151231257827E-17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B28">
         <v>21</v>
       </c>
@@ -1012,8 +1486,26 @@
       <c r="H28">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J28">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="K28">
+        <v>0.16</v>
+      </c>
+      <c r="M28">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B29">
         <v>22</v>
       </c>
@@ -1032,8 +1524,26 @@
       <c r="H29">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J29">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="K29">
+        <v>0.79</v>
+      </c>
+      <c r="M29">
+        <f t="shared" si="9"/>
+        <v>-0.59</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="10"/>
+        <v>-0.58000000000000007</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="11"/>
+        <v>9.9999999999998979E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B30">
         <v>23</v>
       </c>
@@ -1051,6 +1561,24 @@
       </c>
       <c r="H30">
         <v>0.04</v>
+      </c>
+      <c r="J30">
+        <v>0.51</v>
+      </c>
+      <c r="K30">
+        <v>0.04</v>
+      </c>
+      <c r="M30">
+        <f>G30-G23</f>
+        <v>0.62</v>
+      </c>
+      <c r="N30">
+        <f>J30-J23</f>
+        <v>0.62</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="11"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1060,15 +1588,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F66EEEC-6E47-4ABB-93FD-D263C298AAF2}">
-  <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="75.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="75.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -1076,13 +1604,16 @@
         <v>26</v>
       </c>
       <c r="C1" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1090,101 +1621,140 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>-1.75</v>
+        <v>-2.08</v>
       </c>
       <c r="D2">
         <v>3.4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="2">
+        <f>1/D2</f>
+        <v>0.29411764705882354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>-0.36</v>
       </c>
       <c r="D3">
         <v>0.12</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="2">
+        <f t="shared" ref="E3:E10" si="0">1/D3</f>
+        <v>8.3333333333333339</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>5</v>
       </c>
       <c r="C4">
-        <v>0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="D4">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>0.11</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" si="0"/>
+        <v>9.0909090909090917</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>6</v>
       </c>
       <c r="C5">
-        <v>0.76</v>
+        <v>0.42</v>
       </c>
       <c r="D5">
         <v>0.36</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
+        <v>2.7777777777777777</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
-        <v>-0.11</v>
+        <v>-0.45</v>
       </c>
       <c r="D6">
         <v>0.28000000000000003</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="2">
+        <f t="shared" si="0"/>
+        <v>3.5714285714285712</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>7</v>
       </c>
       <c r="C7">
-        <v>-2.0099999999999998</v>
+        <v>-2.35</v>
       </c>
       <c r="D7">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
+        <v>3.3333333333333335</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>8</v>
       </c>
       <c r="C8">
-        <v>-0.14000000000000001</v>
+        <v>-0.49</v>
       </c>
       <c r="D8">
         <v>0.42</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="2">
+        <f t="shared" si="0"/>
+        <v>2.3809523809523809</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>9</v>
       </c>
       <c r="C9">
-        <v>1.61</v>
+        <v>1.31</v>
       </c>
       <c r="D9">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>10</v>
       </c>
       <c r="C10">
-        <v>0.33</v>
+        <v>-0.02</v>
       </c>
       <c r="D10">
         <v>0.18</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" s="2">
+        <f t="shared" si="0"/>
+        <v>5.5555555555555554</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1192,112 +1762,155 @@
         <v>15</v>
       </c>
       <c r="C12">
-        <v>0.56000000000000005</v>
+        <v>-0.05</v>
       </c>
       <c r="D12">
         <v>0.54</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" s="2">
+        <f t="shared" ref="E12:E21" si="1">1/D12</f>
+        <v>1.8518518518518516</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>16</v>
       </c>
       <c r="C13">
-        <v>0.81</v>
+        <v>0.2</v>
       </c>
       <c r="D13">
         <v>0.51</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" s="2">
+        <f t="shared" si="1"/>
+        <v>1.9607843137254901</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>11</v>
       </c>
       <c r="C14">
-        <v>0.47</v>
+        <v>-0.13</v>
       </c>
       <c r="D14">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="2">
+        <f t="shared" si="1"/>
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>17</v>
       </c>
       <c r="C15">
-        <v>0.95</v>
+        <v>0.34</v>
       </c>
       <c r="D15">
         <v>0.41</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="2">
+        <f t="shared" si="1"/>
+        <v>2.4390243902439024</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>18</v>
       </c>
       <c r="C16">
-        <v>7.0000000000000007E-2</v>
+        <v>-0.53</v>
       </c>
       <c r="D16">
         <v>0.36</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="2">
+        <f t="shared" si="1"/>
+        <v>2.7777777777777777</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>19</v>
       </c>
       <c r="C17">
-        <v>0.26</v>
+        <v>-0.34</v>
       </c>
       <c r="D17">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="2">
+        <f t="shared" si="1"/>
+        <v>3.3333333333333335</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="D18">
         <v>0.27</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="2">
+        <f t="shared" si="1"/>
+        <v>3.7037037037037033</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>20</v>
       </c>
       <c r="C19">
-        <v>0.84</v>
+        <v>0.19</v>
       </c>
       <c r="D19">
         <v>0.13</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="2">
+        <f t="shared" si="1"/>
+        <v>7.6923076923076916</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>5</v>
       </c>
       <c r="C20">
-        <v>1.41</v>
+        <v>0.79</v>
       </c>
       <c r="D20">
         <v>1.1000000000000001</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="2">
+        <f t="shared" si="1"/>
+        <v>0.90909090909090906</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>21</v>
       </c>
       <c r="C21">
-        <v>1.63</v>
+        <v>1</v>
       </c>
       <c r="D21">
         <v>0.24</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="2">
+        <f t="shared" si="1"/>
+        <v>4.166666666666667</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1305,87 +1918,119 @@
         <v>4</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="D23">
         <v>0.09</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="2">
+        <f t="shared" ref="E23:E30" si="2">1/D23</f>
+        <v>11.111111111111111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>5</v>
       </c>
       <c r="C24">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="D24">
         <v>7.0000000000000007E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" s="2">
+        <f t="shared" si="2"/>
+        <v>14.285714285714285</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>23</v>
       </c>
       <c r="C25">
-        <v>-1.24</v>
+        <v>-1.32</v>
       </c>
       <c r="D25">
         <v>0.11</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" s="2">
+        <f t="shared" si="2"/>
+        <v>9.0909090909090917</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>24</v>
       </c>
       <c r="C26">
-        <v>-0.17</v>
+        <v>-0.27</v>
       </c>
       <c r="D26">
         <v>0.15</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" s="2">
+        <f t="shared" si="2"/>
+        <v>6.666666666666667</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>6</v>
       </c>
       <c r="C27">
-        <v>0.37</v>
+        <v>0.27</v>
       </c>
       <c r="D27">
         <v>0.1</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="2">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>8</v>
       </c>
       <c r="C28">
-        <v>0.03</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D28">
         <v>0.16</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="2">
+        <f t="shared" si="2"/>
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>9</v>
       </c>
       <c r="C29">
-        <v>0.03</v>
+        <v>-7.0000000000000007E-2</v>
       </c>
       <c r="D29">
         <v>0.79</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="2">
+        <f t="shared" si="2"/>
+        <v>1.2658227848101264</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>25</v>
       </c>
       <c r="C30">
-        <v>0.62</v>
+        <v>0.51</v>
       </c>
       <c r="D30">
         <v>0.04</v>
+      </c>
+      <c r="E30" s="2">
+        <f t="shared" si="2"/>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/data/clean/AR_methods.xlsx
+++ b/data/clean/AR_methods.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bmcgreal\Documents\dissertation\survey\data\clean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D9F221-18A7-496F-86F4-63BBD64F6F12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B1CCA80-1AFF-4778-A89F-58E3E044C8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-57720" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{70F81E01-4849-42CD-AB9B-9414582B1355}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="38">
   <si>
     <t>Chinook</t>
   </si>
@@ -145,6 +145,12 @@
   </si>
   <si>
     <t>Precision</t>
+  </si>
+  <si>
+    <t>CoeffVar</t>
+  </si>
+  <si>
+    <t>Coeff. of Variation</t>
   </si>
 </sst>
 </file>
@@ -504,14 +510,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B32334F8-B11A-4935-8120-0620CA328AA2}">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="75.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B1" t="s">
         <v>12</v>
       </c>
@@ -545,8 +551,11 @@
       <c r="O1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -586,8 +595,11 @@
         <f>ABS(M2-N2)</f>
         <v>2.9999999999999805E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q2">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B3">
         <v>9</v>
       </c>
@@ -613,19 +625,22 @@
         <v>0.12</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M10" si="0">G3-G4</f>
+        <f t="shared" ref="M3:M9" si="0">G3-G4</f>
         <v>-0.27</v>
       </c>
       <c r="N3">
-        <f t="shared" ref="N3:N10" si="1">J3-J4</f>
+        <f t="shared" ref="N3:N9" si="1">J3-J4</f>
         <v>-0.27999999999999997</v>
       </c>
       <c r="O3">
         <f t="shared" ref="O3:O10" si="2">ABS(M3-N3)</f>
         <v>9.9999999999999534E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B4">
         <v>11</v>
       </c>
@@ -662,8 +677,11 @@
         <f t="shared" si="2"/>
         <v>1.0000000000000009E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B5">
         <v>16</v>
       </c>
@@ -700,8 +718,11 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q5">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B6">
         <v>17</v>
       </c>
@@ -738,8 +759,11 @@
         <f t="shared" si="2"/>
         <v>4.4408920985006262E-16</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q6">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B7">
         <v>18</v>
       </c>
@@ -776,8 +800,11 @@
         <f t="shared" si="2"/>
         <v>9.9999999999995648E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B8">
         <v>21</v>
       </c>
@@ -814,8 +841,11 @@
         <f t="shared" si="2"/>
         <v>5.0000000000000044E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q8">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B9">
         <v>22</v>
       </c>
@@ -852,8 +882,11 @@
         <f t="shared" si="2"/>
         <v>5.0000000000000044E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>29</v>
       </c>
@@ -890,8 +923,11 @@
         <f t="shared" si="2"/>
         <v>2.0000000000000018E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q10">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -931,8 +967,11 @@
         <f>ABS(M12-N12)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q12">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>2</v>
       </c>
@@ -969,8 +1008,11 @@
         <f t="shared" ref="O13:O19" si="5">ABS(M13-N13)</f>
         <v>1.0000000000000064E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q13">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>3</v>
       </c>
@@ -1007,8 +1049,11 @@
         <f t="shared" si="5"/>
         <v>9.9999999999999534E-3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q14">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>4</v>
       </c>
@@ -1045,8 +1090,11 @@
         <f t="shared" si="5"/>
         <v>9.9999999999997868E-3</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q15">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>7</v>
       </c>
@@ -1083,8 +1131,11 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q16">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>8</v>
       </c>
@@ -1121,8 +1172,11 @@
         <f t="shared" si="5"/>
         <v>1.9999999999999962E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q17">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>9</v>
       </c>
@@ -1159,8 +1213,11 @@
         <f t="shared" si="5"/>
         <v>2.9999999999999916E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q18">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>10</v>
       </c>
@@ -1197,8 +1254,11 @@
         <f t="shared" si="5"/>
         <v>3.0000000000000138E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q19">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B20">
         <v>11</v>
       </c>
@@ -1224,19 +1284,22 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="M20">
-        <f t="shared" ref="M20:M21" si="6">G20-G21</f>
+        <f t="shared" ref="M20" si="6">G20-G21</f>
         <v>-0.21999999999999997</v>
       </c>
       <c r="N20">
-        <f t="shared" ref="N20:N21" si="7">J20-J21</f>
+        <f t="shared" ref="N20" si="7">J20-J21</f>
         <v>-0.20999999999999996</v>
       </c>
       <c r="O20">
         <f t="shared" ref="O20:O21" si="8">ABS(M20-N20)</f>
         <v>1.0000000000000009E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q20">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B21">
         <v>19</v>
       </c>
@@ -1273,8 +1336,11 @@
         <f t="shared" si="8"/>
         <v>1.9999999999999796E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q21">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1314,8 +1380,11 @@
         <f>ABS(M23-N23)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q23">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B24">
         <v>11</v>
       </c>
@@ -1341,19 +1410,22 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="M24">
-        <f t="shared" ref="M24:M30" si="9">G24-G25</f>
+        <f t="shared" ref="M24:M29" si="9">G24-G25</f>
         <v>1.77</v>
       </c>
       <c r="N24">
-        <f t="shared" ref="N24:N30" si="10">J24-J25</f>
+        <f t="shared" ref="N24:N29" si="10">J24-J25</f>
         <v>1.74</v>
       </c>
       <c r="O24">
         <f t="shared" ref="O24:O30" si="11">ABS(M24-N24)</f>
         <v>3.0000000000000027E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q24">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B25">
         <v>14</v>
       </c>
@@ -1390,8 +1462,11 @@
         <f t="shared" si="11"/>
         <v>2.0000000000000018E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B26">
         <v>15</v>
       </c>
@@ -1428,8 +1503,11 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q26">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B27">
         <v>16</v>
       </c>
@@ -1466,8 +1544,11 @@
         <f t="shared" si="11"/>
         <v>5.5511151231257827E-17</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q27">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B28">
         <v>21</v>
       </c>
@@ -1504,8 +1585,11 @@
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q28">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B29">
         <v>22</v>
       </c>
@@ -1542,8 +1626,11 @@
         <f t="shared" si="11"/>
         <v>9.9999999999998979E-3</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q29">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="B30">
         <v>23</v>
       </c>
@@ -1579,6 +1666,9 @@
       <c r="O30">
         <f t="shared" si="11"/>
         <v>0</v>
+      </c>
+      <c r="Q30">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
@@ -1588,7 +1678,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F66EEEC-6E47-4ABB-93FD-D263C298AAF2}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -1596,7 +1686,7 @@
     <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>27</v>
       </c>
@@ -1612,8 +1702,11 @@
       <c r="E1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1630,8 +1723,11 @@
         <f>1/D2</f>
         <v>0.29411764705882354</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F2">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1645,8 +1741,11 @@
         <f t="shared" ref="E3:E10" si="0">1/D3</f>
         <v>8.3333333333333339</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F3">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>5</v>
       </c>
@@ -1660,8 +1759,11 @@
         <f t="shared" si="0"/>
         <v>9.0909090909090917</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F4">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -1675,8 +1777,11 @@
         <f t="shared" si="0"/>
         <v>2.7777777777777777</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F5">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>13</v>
       </c>
@@ -1690,8 +1795,11 @@
         <f t="shared" si="0"/>
         <v>3.5714285714285712</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F6">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>7</v>
       </c>
@@ -1705,8 +1813,11 @@
         <f t="shared" si="0"/>
         <v>3.3333333333333335</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F7">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>8</v>
       </c>
@@ -1720,8 +1831,11 @@
         <f t="shared" si="0"/>
         <v>2.3809523809523809</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F8">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>9</v>
       </c>
@@ -1735,8 +1849,11 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F9">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>10</v>
       </c>
@@ -1750,11 +1867,14 @@
         <f t="shared" si="0"/>
         <v>5.5555555555555554</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F10">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1771,8 +1891,11 @@
         <f t="shared" ref="E12:E21" si="1">1/D12</f>
         <v>1.8518518518518516</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F12">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -1786,8 +1909,11 @@
         <f t="shared" si="1"/>
         <v>1.9607843137254901</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F13">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>11</v>
       </c>
@@ -1801,8 +1927,11 @@
         <f t="shared" si="1"/>
         <v>2.5</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F14">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>17</v>
       </c>
@@ -1816,8 +1945,11 @@
         <f t="shared" si="1"/>
         <v>2.4390243902439024</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F15">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>18</v>
       </c>
@@ -1831,8 +1963,11 @@
         <f t="shared" si="1"/>
         <v>2.7777777777777777</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F16">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>19</v>
       </c>
@@ -1846,8 +1981,11 @@
         <f t="shared" si="1"/>
         <v>3.3333333333333335</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F17">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
         <v>4</v>
       </c>
@@ -1861,8 +1999,11 @@
         <f t="shared" si="1"/>
         <v>3.7037037037037033</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F18">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -1876,8 +2017,11 @@
         <f t="shared" si="1"/>
         <v>7.6923076923076916</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F19">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>5</v>
       </c>
@@ -1891,8 +2035,11 @@
         <f t="shared" si="1"/>
         <v>0.90909090909090906</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F20">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>21</v>
       </c>
@@ -1906,11 +2053,14 @@
         <f t="shared" si="1"/>
         <v>4.166666666666667</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F21">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -1927,8 +2077,11 @@
         <f t="shared" ref="E23:E30" si="2">1/D23</f>
         <v>11.111111111111111</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F23">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>5</v>
       </c>
@@ -1942,8 +2095,11 @@
         <f t="shared" si="2"/>
         <v>14.285714285714285</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F24">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>23</v>
       </c>
@@ -1957,8 +2113,11 @@
         <f t="shared" si="2"/>
         <v>9.0909090909090917</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>24</v>
       </c>
@@ -1972,8 +2131,11 @@
         <f t="shared" si="2"/>
         <v>6.666666666666667</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F26">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>6</v>
       </c>
@@ -1987,8 +2149,11 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F27">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>8</v>
       </c>
@@ -2002,8 +2167,11 @@
         <f t="shared" si="2"/>
         <v>6.25</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F28">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>9</v>
       </c>
@@ -2017,8 +2185,11 @@
         <f t="shared" si="2"/>
         <v>1.2658227848101264</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="F29">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>25</v>
       </c>
@@ -2031,6 +2202,9 @@
       <c r="E30" s="2">
         <f t="shared" si="2"/>
         <v>25</v>
+      </c>
+      <c r="F30">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>
